--- a/小鸭/港药日货行情日更表.xlsx
+++ b/小鸭/港药日货行情日更表.xlsx
@@ -27,9 +27,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
-  <si>
-    <t>2026/ 1-8港药日货行情参考</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+  <si>
+    <t>2026/ 3-6港药日货行情参考</t>
   </si>
   <si>
     <t>双飞人50ml</t>
@@ -47,18 +47,15 @@
     <t>小粉丸400粒</t>
   </si>
   <si>
-    <t>澳佳宝4倍鱼油60粒</t>
-  </si>
-  <si>
     <t>久光贴40mg</t>
   </si>
   <si>
-    <t>澳佳宝维骨力180粒</t>
-  </si>
-  <si>
     <t>黄道益活络油50ml</t>
   </si>
   <si>
+    <t>bio儿童锌片</t>
+  </si>
+  <si>
     <t>撒隆巴斯140片</t>
   </si>
   <si>
@@ -128,15 +125,12 @@
     <t>珂润高保湿面霜40g</t>
   </si>
   <si>
-    <t>74</t>
+    <t>80</t>
   </si>
   <si>
     <t>芙丽芳丝洗面奶</t>
   </si>
   <si>
-    <t>二代胆碱片120粒</t>
-  </si>
-  <si>
     <t>老人头156枚</t>
   </si>
   <si>
@@ -146,7 +140,7 @@
     <t>老人头78枚</t>
   </si>
   <si>
-    <t>sw辅酶Q10 180粒</t>
+    <t>sw辅酶Q10 180粒150mg</t>
   </si>
   <si>
     <t>幸福001</t>
@@ -155,13 +149,22 @@
     <t>HC辅酶Q10</t>
   </si>
   <si>
+    <t>芳珂卸妆油</t>
+  </si>
+  <si>
     <t>植物金酵素</t>
   </si>
   <si>
     <t>芳珂卸妆油对装</t>
   </si>
   <si>
+    <t>蓝胖子奶粉</t>
+  </si>
+  <si>
     <t>兰芝紫隔离</t>
+  </si>
+  <si>
+    <t>安耐晒小金瓶60ML纸盒</t>
   </si>
 </sst>
 </file>
@@ -174,7 +177,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -187,12 +190,6 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Microsoft YaHei"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFDE3C36"/>
-      <name val="SimSun"/>
       <charset val="134"/>
     </font>
     <font>
@@ -209,12 +206,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="SimSun"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -559,7 +550,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -590,6 +581,19 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
@@ -739,137 +743,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -879,31 +883,25 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1232,320 +1230,324 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3">
-        <v>39</v>
-      </c>
-      <c r="C2" s="3" t="s">
+      <c r="B2" s="2">
+        <v>40</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="3">
-        <v>94</v>
+      <c r="D2" s="2">
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="3">
-        <v>63</v>
-      </c>
-      <c r="C3" s="3" t="s">
+      <c r="B3" s="2">
+        <v>62</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="3">
-        <v>94</v>
+      <c r="D3" s="2">
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="3">
-        <v>40</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="3">
-        <v>54</v>
-      </c>
+      <c r="B4" s="2">
+        <v>43.5</v>
+      </c>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="3">
-        <v>11.2</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="3">
-        <v>90</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="B5" s="2">
+        <v>11</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="3">
-        <v>49.5</v>
-      </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
+        <v>7</v>
+      </c>
+      <c r="B6" s="2">
+        <v>50</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="5">
+        <v>56</v>
+      </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="2">
+        <v>43</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="3">
-        <v>42</v>
-      </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="3">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="5" t="s">
+      <c r="B8" s="2">
+        <v>38</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="3">
-        <v>38</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" s="3">
+      <c r="D8" s="2">
         <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="2">
+        <v>46</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="3">
-        <v>41</v>
-      </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="2">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="D9" s="3">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="B10" s="6">
         <v>13</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="7">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="7">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="3" t="s">
-        <v>18</v>
-      </c>
       <c r="B11" s="6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="8"/>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="3" t="s">
-        <v>19</v>
+      <c r="A12" s="2" t="s">
+        <v>18</v>
       </c>
       <c r="B12" s="6">
         <v>25.5</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>20</v>
+      <c r="C12" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="D12" s="7">
         <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="2">
+        <v>42</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="3">
-        <v>41.5</v>
-      </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="7">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D13" s="7">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="3" t="s">
+      <c r="B14" s="2">
+        <v>555</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="3">
-        <v>542</v>
-      </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="3">
-        <v>64.5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D15" s="3">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="3" t="s">
+      <c r="B16" s="2">
+        <v>22</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="3">
-        <v>21</v>
-      </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D16" s="3">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="3" t="s">
+      <c r="B17" s="2">
+        <v>53</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B17" s="3">
-        <v>47</v>
-      </c>
-      <c r="C17" s="3" t="s">
+      <c r="D17" s="2">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D17" s="3">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="3" t="s">
+      <c r="B18" s="2">
+        <v>32</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="3">
-        <v>28.5</v>
-      </c>
-      <c r="C18" s="3" t="s">
+      <c r="D18" s="2">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D18" s="3">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="3" t="s">
+      <c r="B19" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="3" t="s">
+      <c r="B20" s="2">
+        <v>56</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B20" s="3">
-        <v>55</v>
-      </c>
-      <c r="C20" s="3" t="s">
+      <c r="B21" s="2">
+        <v>26</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D20" s="3"/>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="3" t="s">
+      <c r="D21" s="2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B21" s="3">
-        <v>23</v>
-      </c>
-      <c r="C21" s="3" t="s">
+      <c r="B22" s="2">
+        <v>29</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D21" s="3">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="3" t="s">
+      <c r="D22" s="2">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="3">
-        <v>24.5</v>
-      </c>
-      <c r="C22" s="3" t="s">
+      <c r="B23" s="2">
+        <v>31</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D22" s="3">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="3" t="s">
+      <c r="D23" s="3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B23" s="3">
-        <v>28.5</v>
-      </c>
-      <c r="C23" s="10" t="s">
+      <c r="B24" s="2">
+        <v>74</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D23" s="10">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="3"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="10" t="s">
+      <c r="D24" s="3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D24" s="10">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="10" t="s">
+      <c r="B25" s="3">
+        <v>147</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B25" s="10">
-        <v>133</v>
-      </c>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
+      <c r="D25" s="3">
+        <v>74</v>
+      </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B26" s="3">
-        <v>54</v>
-      </c>
-      <c r="C26" s="4"/>
+      <c r="B26" s="2">
+        <v>63</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>45</v>
+      </c>
       <c r="D26" s="4"/>
     </row>
   </sheetData>
